--- a/Production Trackers/MPLY_Article_Production.xlsx
+++ b/Production Trackers/MPLY_Article_Production.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2188,6 +2188,1152 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Regulatory Moat</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>regulatory moat</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>regulatory barriers to entry; regulatory advantage; regulated monopoly</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>licenses, regulation, exclusivity, compliance</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Regulatory exclusivity and barriers can create durable competitive positioning, one of the characteristics stated in MPLY's investment approach.</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Regulatory Moat? Credit Rating Agencies Explained</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>A regulatory moat exists when government, not the market, limits competition. Credit rating agencies show how a 1975 SEC designation still concentrates an industry.</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Credit rating revenue concentration donut chart (S&amp;P/Moody's/Fitch 91%), verified data.</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'barriers to entry' -&gt; What Are Barriers to Entry in Business (No.6)</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>congress.gov/crs-product/IF11916; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>#RegulatoryMoat #EconomicMoat #CompetitiveAdvantage #BarriersToEntry #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>012_What_Is_a_Regulatory_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Economies of Scale vs Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>economies of scale competitive advantage</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>economies of scale moat; scale advantage examples</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>fixed costs, operating leverage, unit costs</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Scale can contribute to a durable competitive advantage, but scale alone does not necessarily create a moat.</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Economies of Scale vs Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Scale lowers costs, but it doesn't always create a moat. Amazon's fulfillment network versus commodity steel production shows the difference.</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; economies-of-scale chart already exists for article 013, no new verified data warranted a second chart.</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'cost advantage moat' -&gt; What Is a Cost Advantage Moat (No.13)</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>#EconomiesOfScale #CompetitiveAdvantage #EconomicMoat #MPLY #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>014_Economies_of_Scale_vs_Competitive_Advantage.docx</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>Comparison archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Economies of Scope vs Economies of Scale</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>economies of scope vs economies of scale</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>economies of scope examples; economies of scale examples</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>shared resources, cost structure, diversification</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Business Economics</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Understanding different sources of business advantage helps readers evaluate whether scale or scope creates durable economic benefits.</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Economies of Scope vs Economies of Scale</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Scope and scale both lower costs but through different mechanisms. P&amp;G's shared resources across categories illustrate scope; a single-product plant illustrates scale.</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; checklist-style bullets in-text served the comparison without a separate chart.</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>#EconomiesOfScope #EconomiesOfScale #BusinessEconomics #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>015_Economies_of_Scope_vs_Economies_of_Scale.docx</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>Checklist/Research Guide archetype; Business Economics cluster (not Economic Moats).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Learning Curve Advantage</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>learning curve advantage</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>learning curve competitive advantage; experience curve moat</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>experience effects, productivity, unit costs</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Learning effects can improve cost and operational advantages over time, which can contribute to durable competitive positioning.</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Learning Curve Advantage</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>A learning curve advantage comes from accumulated production experience, not current volume. Wright's 1936 aircraft study and solar panel costs show the pattern.</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Illustrative learning-curve (Wright's Law shape) chart.</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'economies of scale' -&gt; Economies of Scale vs Competitive Advantage (No.14)</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>ourworldindata.org/learning-curve; en.wikipedia.org/wiki/Experience_curve_effect</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>#LearningCurve #ExperienceCurve #CompetitiveAdvantage #EconomicMoat #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>016_What_Is_a_Learning_Curve_Advantage.docx</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>Mechanism-Based archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Distribution Moat</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>distribution moat</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>distribution competitive advantage; distribution advantage examples</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>customer acquisition, channels, reach, scale</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Distribution strength can make customer acquisition harder for competitors and can support durable competitive positioning.</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Distribution Moat</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>A distribution moat comes from customer access a competitor can't easily replicate. Coca-Cola's global bottling network shows how it works and where it's weakening.</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating distribution-reach figures.</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'economic moat examples' -&gt; Economic Moat Examples (No.3)</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>#DistributionMoat #EconomicMoat #CompetitiveAdvantage #SupplyChain #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>017_What_Is_a_Distribution_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>Case Study/Examples archetype; Coca-Cola distribution angle distinct from article 003's brand angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>What Is an Ecosystem Moat</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ecosystem moat</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>business ecosystem competitive advantage; ecosystem strategy</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>platform, cross-selling, switching costs, integration</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Integrated ecosystems can increase switching costs and customer dependence, making the concept relevant to evaluating durable business advantages.</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>What Is an Ecosystem Moat? Apple's Lock-In Explained</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>An ecosystem moat comes from multiple connected products that work better together. Apple's hardware, software, and services lock-in shows how it compounds.</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>Hub-and-spoke ecosystem conceptual diagram.</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'switching costs' -&gt; What Are Switching Costs and Why Do They Matter (No.4)</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>#EcosystemMoat #EconomicMoat #CompetitiveAdvantage #SwitchingCosts #MPLY #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>018_What_Is_an_Ecosystem_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype; FAQ included (broad, high-intent topic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Data Moat</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>data moat</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>data competitive advantage; proprietary data moat; data advantage</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>proprietary data, machine learning, network effects</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Proprietary data can contribute to competitive advantage when it is difficult to replicate and creates measurable economic benefits.</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Data Moat</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>A data moat exists when proprietary data creates a feedback loop that improves a product. Google's search quality shows how it works, and when it doesn't.</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating data-scale figures.</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'network effects' -&gt; Network Effects Explained (No.5)</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>#DataMoat #CompetitiveAdvantage #EconomicMoat #MachineLearning #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>019_What_Is_a_Data_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>Investor Framework archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>What Is an Intellectual Property Moat</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>intellectual property moat</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>IP competitive advantage; patent moat; intellectual property advantage</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>patents, licensing, proprietary technology</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Intellectual property can create barriers to entry and regulatory or legal exclusivity that may support durable competitive positioning.</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>What Is an Intellectual Property Moat</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>An IP moat is a legally protected advantage with a known expiration date. Here's how patents work, the pharmaceutical patent cliff, and trade secrets.</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; a patent-lifecycle timeline was considered but the prose Timeline/Evolution structure already covers this without a chart.</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'barriers to entry' -&gt; What Are Barriers to Entry in Business (No.6)</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>#IntellectualProperty #PatentMoat #EconomicMoat #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>020_What_Is_an_Intellectual_Property_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>Timeline/Evolution archetype; FAQ included (broad, high-intent topic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Scale Moat</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>scale moat</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>scale advantage moat; scale economies business</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>economies of scale, fixed costs, market share</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Scale can strengthen cost advantages and market position, but its durability depends on how difficult it is for competitors to replicate.</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Scale Moat? Amazon's Flywheel Explained</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>A scale moat is self-reinforcing, not just cost-reducing. Amazon's flywheel shows how scale can compound rather than just lower costs.</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; the flywheel concept is well conveyed in prose; a circular-diagram chart was considered but judged unnecessary given No.18's ecosystem diagram already fills that visual role in this batch.</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'economies of scale' -&gt; Economies of Scale vs Competitive Advantage (No.14)</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>#ScaleMoat #EconomicMoat #CompetitiveAdvantage #MPLY #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>021_What_Is_a_Scale_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>Mechanism-Based archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Market Share Moat</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>market share moat</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>market share competitive advantage; dominant market share</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>market leadership, scale, distribution, brand</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Market leadership can matter when it reflects durable competitive advantages rather than simply a temporary lead.</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Market Share Moat? Lessons From Nokia</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Dominant market share looks like a moat but isn't automatically one. Nokia's collapse from 51% to under 3% share shows why the underlying driver matters more.</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>Nokia 2007 vs 2013 market share collapse bar chart, verified data.</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'second mover advantage' -&gt; What Is a Second Mover Advantage (No.33)</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>en.wikipedia.org/wiki/The_Decline_and_Fall_of_Nokia; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>#MarketShare #EconomicMoat #CompetitiveAdvantage #MPLY #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>022_What_Is_a_Market_Share_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>Myth vs. Reality archetype.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Production Trackers/MPLY_Article_Production.xlsx
+++ b/Production Trackers/MPLY_Article_Production.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3334,6 +3334,1148 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>How Switching Costs Protect Recurring Revenue</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>switching costs recurring revenue</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>switching costs subscription business; recurring revenue moat</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>retention, churn, customer lock-in</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Switching costs can help explain why recurring revenue is durable, making the mechanism relevant to MPLY's focus on defensible businesses.</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>How Switching Costs Protect Recurring Revenue</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>A subscription is just a billing pattern. Switching costs are what actually protect recurring revenue, illustrated with cloud infrastructure lock-in.</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating churn/migration-cost figures.</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'switching costs' -&gt; What Are Switching Costs and Why Do They Matter (No.4); Anchor 'recurring revenue moat' -&gt; How Recurring Revenue Creates a Business Moat (No.9)</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>#SwitchingCosts #RecurringRevenue #EconomicMoat #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>023_How_Switching_Costs_Protect_Recurring_Revenue.docx</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>Mechanism-Based archetype; fresh AWS/cloud example distinct from prior SAP/Adobe examples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>How Pricing Power Protects Profit Margins</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>pricing power profit margins</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>pricing power margins; margin protection; pricing power businesses</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>gross margin, operating margin, inflation</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Sustained pricing power can protect economics against cost pressure and is relevant to assessing durable competitive strength.</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>How Pricing Power Protects Profit Margins</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Pricing power is the specific mechanism that protects margins during cost inflation. Airline fuel surcharges show how the pass-through works.</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating margin figures.</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'pricing power' -&gt; What Is Pricing Power and Why It Matters for Investors (No.1)</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>#PricingPower #ProfitMargins #EconomicMoat #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>024_How_Pricing_Power_Protects_Profit_Margins.docx</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype; margin-mechanics angle distinct from No.1's general definition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>How to Identify a Durable Economic Moat</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>how to identify an economic moat</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>economic moat checklist; moat analysis; durable competitive advantage</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>pricing power, switching costs, network effects, barriers to entry</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Economic Moats</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>How-to / Research</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>A practical moat framework overlaps closely with the competitive characteristics described in MPLY's investment approach.</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>How to Identify a Durable Economic Moat</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>A practical checklist for identifying a durable moat: financial signals, naming the specific mechanism, stress-testing against a real challenger.</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>Reused No.026's ROIC-WACC chart as a supporting visual rather than building a duplicate.</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'competitive moat' -&gt; What Is a Competitive Moat in Investing (No.2)</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>#EconomicMoat #MoatAnalysis #CompetitiveAdvantage #StockResearch #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>025_How_to_Identify_a_Durable_Economic_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>Checklist/Research Guide archetype; FAQ included (broad how-to topic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>How to Analyze Competitive Advantage in Stocks</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>analyze competitive advantage stocks</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>competitive advantage analysis; stock moat analysis</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>business quality, moat, profitability</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>How-to / Research</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Analyzing durable competitive advantages is central to understanding the type of companies MPLY seeks to identify.</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>How to Analyze Competitive Advantage in Stocks</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>A quantitative framework for analyzing competitive advantage: the ROIC-WACC spread, margin trends, and free cash flow conversion.</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>Illustrative ROIC vs WACC spread bar chart.</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'how to identify a moat' -&gt; How to Identify a Durable Economic Moat (No.25)</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>#StockAnalysis #CompetitiveAdvantage #ROIC #EconomicMoat #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>026_How_to_Analyze_Competitive_Advantage_in_Stocks.docx</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>Investor Framework archetype (quantitative), distinct from No.25's qualitative checklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>What Makes a Company a Market Leader</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>market leader competitive advantage</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>market leadership examples; market leader moat</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>market share, brand, scale, distribution</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Market leadership can reflect durable advantages such as brand strength, scale, distribution or network effects.</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>What Makes a Company a Market Leader</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Market leadership isn't always the same as market share. Whole Foods' premium-grocery leadership shows how perception-based leadership works.</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating share figures.</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'market share moat' -&gt; What Is a Market Share Moat (No.22)</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>#MarketLeader #CompetitiveAdvantage #BrandStrategy #MPLY #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>027_What_Makes_a_Company_a_Market_Leader.docx</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>Case Study/Examples archetype; Whole Foods angle distinct from No.22's Nokia share-collapse case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Market Dominance vs Monopoly: What Is the Difference</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>market dominance vs monopoly</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>market dominance definition; monopoly vs market leader</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>competition, market share, barriers to entry</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Market dominance and monopoly economics help explain how barriers and competitive advantages can create durable market positions.</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Market Dominance vs Monopoly: What Is the Difference</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Market dominance and monopoly aren't the same. The Sherman Act's legal standard and the economic spectrum from competition to monopoly, explained.</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>Market structure spectrum conceptual diagram (perfect competition to monopoly).</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr"/>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>ftc.gov/advice-guidance/competition-guidance/guide-antitrust-laws/antitrust-laws; en.wikipedia.org/wiki/Sherman_Antitrust_Act; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>#MarketDominance #Monopoly #Antitrust #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>028_Market_Dominance_vs_Monopoly.docx</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>Comparison archetype; direct legal/economic content given MPLY's own monopoly/oligopoly framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Durable Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>durable competitive advantage</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>sustainable competitive advantage; lasting competitive advantage</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>economic moat, pricing power, switching costs</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Durable competitive advantage is closely aligned with the business characteristics MPLY seeks in its stated investment approach.</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Durable Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Durable competitive advantage and economic moat are the same idea from two traditions. Porter's 1980s strategy work and Buffett's moat term, compared.</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>Porter/Buffett terminology timeline (1980, 1985, 1986), verified dates.</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'competitive moat' -&gt; What Is a Competitive Moat in Investing (No.2)</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>en.wikipedia.org/wiki/Competitive_advantage; en.wikipedia.org/wiki/Economic_moat; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>#CompetitiveAdvantage #EconomicMoat #MichaelPorter #WarrenBuffett #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>029_What_Is_a_Durable_Competitive_Advantage.docx</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>Timeline/Evolution archetype; terminology-history angle distinct from No.2's definitional treatment. FAQ included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Sustainable Competitive Advantage Examples</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>sustainable competitive advantage examples</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>competitive advantage examples; durable moat examples</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>brand, network effects, switching costs</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Examples</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Examples of sustainable advantages help readers understand the characteristics that may support long-term business strength.</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Sustainable Competitive Advantage Examples</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Three genuinely different sources of sustainable advantage: UPS's distribution density, NYSE/Nasdaq's network effects, and Intel's architecture lock-in.</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded per Strong-thematic depth rule)</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating market-share figures.</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'economic moat examples' -&gt; Economic Moat Examples (No.3)</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>#CompetitiveAdvantage #EconomicMoat #NetworkEffects #DistributionMoat #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>030_Sustainable_Competitive_Advantage_Examples.docx</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>Case Study/Examples archetype; UPS/NYSE-Nasdaq/Intel fresh examples distinct from No.3's Coca-Cola/Visa/ASML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage vs Competitive Edge</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>competitive advantage vs competitive edge</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>competitive advantage definition; business edge</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>moat, differentiation, market position</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>The distinction helps explain why some business advantages are more durable than others.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage vs Competitive Edge</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>An edge is a current, often temporary lead. An advantage is structural and durable. Here's the practical test for telling them apart.</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; conceptual, not numeric topic, no chart warranted.</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr"/>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>#CompetitiveAdvantage #CompetitiveEdge #BusinessStrategy #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>031_Competitive_Advantage_vs_Competitive_Edge.docx</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>Comparison archetype; Moderate relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>What Is a First Mover Advantage</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>first mover advantage</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>first mover advantage examples; first mover moat</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>network effects, brand recognition, switching costs</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>First-mover status can matter when it develops into a durable advantage such as network effects or switching costs.</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>What Is a First Mover Advantage</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Being first is a temporary head start, not a moat by itself. eBay and Craigslist show when it converts into something durable, and when it doesn't.</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; the pioneer-vs-second-mover timeline chart on No.33 already covers this angle visually.</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'second mover advantage' -&gt; What Is a Second Mover Advantage (No.33)</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>en.wikipedia.org/wiki/EBay; en.wikipedia.org/wiki/Craigslist; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>#FirstMoverAdvantage #CompetitiveAdvantage #NetworkEffects #BusinessStrategy #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>032_What_Is_a_First_Mover_Advantage.docx</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>Mechanism-Based archetype; direct complement to No.33 (second mover), fresh eBay/Craigslist examples.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Production Trackers/MPLY_Article_Production.xlsx
+++ b/Production Trackers/MPLY_Article_Production.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4476,6 +4476,1152 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>How Brand Strength Creates Pricing Power</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>brand strength pricing power</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>brand pricing power; brand moat; premium pricing</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>brand equity, customer loyalty, differentiation</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Brand strength and pricing power are directly relevant to evaluating durable competitive positioning.</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>How Brand Strength Creates Pricing Power</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Brand-driven pricing power is a specific mechanism, not just customer loyalty. Veblen goods and risk-reduction pricing explain how it works.</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset available without fabricating price-premium figures.</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'brand loyalty' -&gt; Brand Loyalty as a Competitive Advantage (No.7); Anchor 'pricing power' -&gt; What Is Pricing Power (No.1)</t>
+        </is>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>#BrandStrength #PricingPower #EconomicMoat #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>034_How_Brand_Strength_Creates_Pricing_Power.docx</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>Mechanism-Based archetype; Veblen goods angle distinct from No.7's brand loyalty and No.1's general pricing power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>How Customer Lock-In Creates a Moat</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>customer lock in moat</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>customer lock-in examples; customer lock in strategy</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>switching costs, retention, recurring revenue</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Customer lock-in can reflect switching costs and other mechanisms that make competitive displacement harder.</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>How Customer Lock-In Creates a Moat</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Not all customer lock-in is equal. A taxonomy of four types, contractual, technical, data, and habit, and why the distinction changes how durable it is.</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>Reused No.026's ROIC-WACC chart as supporting evidence rather than building a duplicate.</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'switching costs' -&gt; What Are Switching Costs (No.4)</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>#CustomerLockIn #SwitchingCosts #EconomicMoat #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>035_How_Customer_Lock_In_Creates_a_Moat.docx</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>Checklist/Research Guide archetype; lock-in taxonomy distinct from prior single-mechanism switching-cost articles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>How Network Effects Create Market Dominance</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>network effects market dominance</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>network effect market power; network effect moat</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>platform economics, user growth, barriers to entry</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Network effects can reinforce market position and create barriers that are relevant to durable competitive advantage analysis.</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>How Network Effects Create Market Dominance</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>VHS beat Betamax despite a one-year head start and worse picture quality. The format war shows how fast a network effect can tip a market.</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>VHS vs Betamax market share chart, verified data (1980/1981/1987).</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'network effects' -&gt; Network Effects Explained (No.5)</t>
+        </is>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>en.wikipedia.org/wiki/Videotape_format_war; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>#NetworkEffects #MarketDominance #EconomicMoat #CompetitiveAdvantage #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>036_How_Network_Effects_Create_Market_Dominance.docx</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>Case Study/Examples archetype; VHS/Betamax fresh example distinct from Friendster (No.11) and prior network-effect articles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>How Barriers to Entry Protect Incumbent Companies</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>barriers to entry incumbent companies</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>entry barriers examples; incumbent advantage</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>capital, regulation, scale, network effects</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Competitive Advantage</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Barriers to entry are one of the clearest mechanisms through which durable competitive positioning can persist.</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>How Barriers to Entry Protect Incumbent Companies</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Heathrow operates at 99% capacity and British Airways holds 51% of its slots. When a resource is physically capped, incumbency becomes the barrier.</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>Heathrow slot concentration bar chart, verified data.</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'barriers to entry' -&gt; What Are Barriers to Entry in Business (No.6)</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>iba.aero; commonslibrary.parliament.uk; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>#BarriersToEntry #EconomicMoat #CompetitiveAdvantage #MarketStructure #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>037_How_Barriers_to_Entry_Protect_Incumbent_Companies.docx</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype; scarce-resource/airport-slot angle distinct from No.6's general capital/regulatory barriers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>What Is a High Quality Business</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>high quality business</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>quality business stocks; business quality investing</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>ROIC, margins, cash flow, competitive advantage</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Business quality often depends on durable competitive advantages and economics, concepts relevant to MPLY's approach.</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>What Is a High Quality Business</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>A three-pillar test for business quality: profitability, capital efficiency, and balance sheet strength, and why all three need to hold together.</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; conceptual framework already clear in prose, no chart warranted.</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'competitive moat' -&gt; What Is a Competitive Moat in Investing (No.2)</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>#QualityInvesting #BusinessQuality #ROIC #EconomicMoat #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>038_What_Is_a_High_Quality_Business.docx</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype; FAQ included (broad definitional topic, new Quality Investing cluster).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>What Is Quality Investing</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>quality investing</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>quality investing strategy; quality stocks</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>ROIC, profitability, balance sheet, moat</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Quality investing provides context for evaluating businesses with durable economics, which overlaps with MPLY's stated focus.</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>What Is Quality Investing</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Quality investing traces from Graham's 1949 deep-value approach through Buffett and Munger's 1959 shift to Novy-Marx's 2013 academic validation.</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>Quality investing history timeline (1949/1959/2013), verified dates.</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'high quality business' -&gt; What Is a High Quality Business (No.38)</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>acquirersmultiple.com; top1000funds.com; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>#QualityInvesting #WarrenBuffett #ValueInvesting #EconomicMoat #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>039_What_Is_Quality_Investing.docx</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>Timeline/Evolution archetype; genuinely new content (investing-style history) distinct from No.38's business-characteristics framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>What Is Return on Invested Capital</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>return on invested capital</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>ROIC explained; high ROIC companies; ROIC investing</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>capital efficiency, profitability, moat</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>ROIC can help assess the economic quality of a business, although a high ROIC alone does not prove a durable moat.</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>What Is Return on Invested Capital</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>ROIC measures how efficiently a company turns invested capital into profit. The formula, what counts as strong, and its key limitation.</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>Reused No.026's ROIC-WACC chart concept in prose; no new chart needed for a pure definitional piece.</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'how to analyze competitive advantage' -&gt; How to Analyze Competitive Advantage in Stocks (No.26)</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>#ROIC #QualityInvesting #CapitalEfficiency #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>040_What_Is_Return_on_Invested_Capital.docx</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype; pure definition/formula, distinct from No.26's application-focused ROIC-WACC framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Why High ROIC Matters for Investors</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>why high ROIC matters</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>high ROIC stocks; ROIC competitive advantage</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>capital efficiency, margins, reinvestment</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Research</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>Sustained high returns on capital can be evidence of strong economics when supported by durable competitive advantages.</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Why High ROIC Matters for Investors</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>High ROIC compounds shareholder value faster when reinvested. Why growth without checking the return it earns can mislead investors.</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; reinvestment-multiplier concept adequately conveyed in prose.</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'what is ROIC' -&gt; What Is Return on Invested Capital (No.40)</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>#ROIC #QualityInvesting #CompoundingReturns #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>041_Why_High_ROIC_Matters_for_Investors.docx</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>Investor Framework archetype; "why it matters" angle distinct from No.40's definitional piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>What Is Free Cash Flow and Why Does It Matter</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>free cash flow</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>free cash flow explained; FCF investing; free cash flow yield</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>cash generation, capital expenditures, operating cash flow</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Cash generation is an important part of evaluating business quality, but FCF should be considered alongside the durability of the competitive advantage.</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>What Is Free Cash Flow and Why Does It Matter</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow is the actual cash a business generates after capital expenditures. The formula and why it can tell a different story than earnings.</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>Reused No.043's FCF waterfall chart concept; kept this article text-only to avoid duplicating the visual.</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'free cash flow vs net income' -&gt; Free Cash Flow vs Net Income (No.43)</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>#FreeCashFlow #QualityInvesting #CashFlow #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>042_What_Is_Free_Cash_Flow_and_Why_Does_It_Matter.docx</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Free Cash Flow vs Net Income</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>free cash flow vs net income</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>FCF vs net income; cash flow vs earnings</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>accrual accounting, capital expenditures, earnings quality</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>The distinction helps readers evaluate business economics, but an MPLY connection would be secondary to the accounting explanation.</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Free Cash Flow vs Net Income</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Net income follows accrual accounting; free cash flow tracks actual cash. Where the two diverge, and what that gap signals.</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Omit</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>None (per brief; respected, no genuine incidental connection found)</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>FCF-from-net-income waterfall bridge chart, illustrative.</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'what is free cash flow' -&gt; What Is Free Cash Flow and Why Does It Matter (No.42)</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="inlineStr"/>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>#FreeCashFlow #NetIncome #Accounting #QualityInvesting #Investing</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>043_Free_Cash_Flow_vs_Net_Income.docx</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>Comparison archetype. Brief tagged Indirect/None and, unlike No.3/No.33, no genuine incidental MPLY connection was found in the body; Omit respected as the correct call, with one brief acknowledging sentence rather than a full section or hashtag.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Production Trackers/MPLY_Article_Production.xlsx
+++ b/Production Trackers/MPLY_Article_Production.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5622,6 +5622,1144 @@
         </is>
       </c>
     </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>What Is Earnings Quality</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>earnings quality</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>earnings quality analysis; quality of earnings</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>cash conversion, accruals, revenue recognition</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>Earnings quality is useful for fundamental research but does not by itself create a direct MPLY connection.</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>What Is Earnings Quality</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Earnings quality measures how much of reported profit is backed by real cash versus accounting estimates. The accrual gap and where weak quality shows up.</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Omit</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>None (per brief; respected)</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; no verified numeric dataset warranted without fabricating accrual figures.</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>#EarningsQuality #QualityInvesting #Accounting #FundamentalAnalysis #Investing</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>044_What_Is_Earnings_Quality.docx</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Cash Conversion Cycle</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>cash conversion cycle</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>cash conversion cycle explained; CCC formula</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>inventory, receivables, payables, working capital</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Business Economics</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Working capital efficiency can help evaluate operating quality but is not itself a defining MPLY characteristic.</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Cash Conversion Cycle</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>The cash conversion cycle measures how fast a business gets its cash back. The DIO+DSO-DPO formula and what a negative cycle means.</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Omit</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>None (per brief; respected)</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; formula explained clearly in prose, no chart warranted.</t>
+        </is>
+      </c>
+      <c r="R47" s="4" t="inlineStr"/>
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>#CashConversionCycle #WorkingCapital #BusinessEconomics #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="inlineStr">
+        <is>
+          <t>045_What_Is_a_Cash_Conversion_Cycle.docx</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>What Is Operating Leverage</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>operating leverage</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>operating leverage examples; operating leverage stocks</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>fixed costs, margins, revenue growth</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Business Economics</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Operating leverage can affect profitability but does not necessarily indicate a durable competitive advantage.</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>What Is Operating Leverage</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Operating leverage describes how much profit swings relative to revenue based on fixed versus variable cost mix. Why it amplifies both gains and losses.</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Omit</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>None (per brief; respected)</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; mechanism explained clearly in prose, no chart warranted.</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>#OperatingLeverage #BusinessEconomics #Profitability #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="inlineStr">
+        <is>
+          <t>046_What_Is_Operating_Leverage.docx</t>
+        </is>
+      </c>
+      <c r="V48" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W48" s="4" t="inlineStr">
+        <is>
+          <t>Mechanism-Based archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>What Is Gross Margin and Why It Matters</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>gross margin</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>gross margin explained; high gross margin business</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>pricing power, cost structure, unit economics</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Gross margin can provide evidence about pricing power and business economics, both useful in evaluating competitive strength.</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>What Is Gross Margin and Why It Matters</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Gross margin shows how much of each sales dollar survives direct production costs. The formula and why the trend matters more than one reading.</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; formula and concept clear in prose without a chart.</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'pricing power' -&gt; What Is Pricing Power (No.1)</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>#GrossMargin #QualityInvesting #PricingPower #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>047_What_Is_Gross_Margin_and_Why_It_Matters.docx</t>
+        </is>
+      </c>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>What Is Operating Margin</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>operating margin</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>operating margin explained; operating margin analysis</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>profitability, operating leverage, cost structure</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Quality Investing</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Operating margins can help assess business economics, but durability matters more than a single margin reading.</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>What Is Operating Margin</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Operating margin captures profit after both production costs and operating expenses. The gap between gross and operating margin, and what it reveals.</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; concept clear in prose without a chart.</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'gross margin' -&gt; What Is Gross Margin and Why It Matters (No.47)</t>
+        </is>
+      </c>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>#OperatingMargin #QualityInvesting #Profitability #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>048_What_Is_Operating_Margin.docx</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Recurring Revenue Business</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>recurring revenue business</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>recurring revenue model; subscription business; recurring revenue stocks</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>subscriptions, retention, churn, predictability</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Business Models</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Recurring revenue can support predictable economics, while the durability of retention and switching costs determines whether it becomes a moat.</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Recurring Revenue Business</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>A recurring revenue business is structured around repeated payments, but predictability and durability are separate questions. Where the moat question begins.</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section, expanded per Strong-thematic rule</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention (per brief; expanded)</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; conceptual, no chart warranted.</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'recurring revenue moat' -&gt; How Recurring Revenue Creates a Business Moat (No.9)</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>#RecurringRevenue #BusinessModels #SubscriptionBusiness #EconomicMoat #MPLY #Investing</t>
+        </is>
+      </c>
+      <c r="U51" s="4" t="inlineStr">
+        <is>
+          <t>049_What_Is_a_Recurring_Revenue_Business.docx</t>
+        </is>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype; business-model-category framing distinct from No.9's moat-mechanism analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>What Is Subscription Business Model</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>subscription business model</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>subscription revenue model; subscription economics</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>recurring revenue, churn, retention, customer lifetime value</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Business Models</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Subscription economics can support recurring revenue and customer relationships, but the competitive advantage depends on the underlying business model.</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Subscription Business Model</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>A subscription business model is one implementation of recurring revenue, defined by its own metrics: CAC, churn, and lifetime value.</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; conceptual, no chart warranted.</t>
+        </is>
+      </c>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'recurring revenue business' -&gt; What Is a Recurring Revenue Business (No.49)</t>
+        </is>
+      </c>
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>#SubscriptionBusiness #BusinessModels #RecurringRevenue #Churn #Investing</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr">
+        <is>
+          <t>050_What_Is_Subscription_Business_Model.docx</t>
+        </is>
+      </c>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W52" s="4" t="inlineStr">
+        <is>
+          <t>Comparison archetype; operating-mechanics angle distinct from No.49's category definition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>What Is Customer Lifetime Value</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>customer lifetime value</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>CLV explained; customer lifetime value formula</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>retention, churn, acquisition cost, recurring revenue</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Business Economics</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>High customer lifetime value can reflect retention and pricing economics, which are useful indicators when evaluating business quality.</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>What Is Customer Lifetime Value</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>Customer lifetime value estimates total expected revenue from a customer relationship. The formula and why it's especially sensitive to churn.</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>Brief Mention</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; formula clear in prose without a chart.</t>
+        </is>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'CAC vs LTV' -&gt; Customer Acquisition Cost vs Lifetime Value (No.52)</t>
+        </is>
+      </c>
+      <c r="S53" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>#CustomerLifetimeValue #BusinessEconomics #Retention #Investing #Fundamentals</t>
+        </is>
+      </c>
+      <c r="U53" s="4" t="inlineStr">
+        <is>
+          <t>051_What_Is_Customer_Lifetime_Value.docx</t>
+        </is>
+      </c>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W53" s="4" t="inlineStr">
+        <is>
+          <t>Explainer archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Customer Acquisition Cost vs Lifetime Value</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>CAC vs LTV</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>customer acquisition cost vs lifetime value; LTV CAC ratio</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>unit economics, retention, payback period</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Business Economics</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>The relationship is useful for understanding business economics, but it is not inherently an MPLY investment characteristic.</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>Customer Acquisition Cost vs Lifetime Value</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>The LTV:CAC ratio and payback period together determine whether a growth strategy is actually economical, not either metric alone.</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Omit</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>None (per brief; respected)</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated; ratio/payback concepts clear in prose without a chart.</t>
+        </is>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'customer lifetime value' -&gt; What Is Customer Lifetime Value (No.51)</t>
+        </is>
+      </c>
+      <c r="S54" s="4" t="inlineStr">
+        <is>
+          <t>strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>#CAC #CustomerLifetimeValue #UnitEconomics #BusinessEconomics #Investing</t>
+        </is>
+      </c>
+      <c r="U54" s="4" t="inlineStr">
+        <is>
+          <t>052_Customer_Acquisition_Cost_vs_Lifetime_Value.docx</t>
+        </is>
+      </c>
+      <c r="V54" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W54" s="4" t="inlineStr">
+        <is>
+          <t>Comparison archetype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Set 01</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Monopoly Business</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>monopoly business</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>monopoly examples; monopoly companies; monopoly economics</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>market power, barriers to entry, pricing power</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Market Dominance</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Informational / Definition</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Strong thematic</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Monopoly economics provide a direct framework for understanding barriers to entry, pricing power and durable market dominance.</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>What Is a Monopoly Business? The De Beers Case</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>De Beers controlled up to 90% of world diamond production for decades. How the monopoly formed, and how it eroded despite near-total market control.</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>Contextual Section</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>De Beers market share decline bar chart (peak vs. early-2000s), verified data.</t>
+        </is>
+      </c>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>Anchor 'market dominance vs monopoly' -&gt; Market Dominance vs Monopoly (No.28)</t>
+        </is>
+      </c>
+      <c r="S55" s="4" t="inlineStr">
+        <is>
+          <t>en.wikipedia.org/wiki/De_Beers; strategysharesetfs.com/mply</t>
+        </is>
+      </c>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>#Monopoly #MarketDominance #MPLY #EconomicMoat #CompetitiveAdvantage #Investing</t>
+        </is>
+      </c>
+      <c r="U55" s="4" t="inlineStr">
+        <is>
+          <t>053_What_Is_a_Monopoly_Business.docx</t>
+        </is>
+      </c>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W55" s="4" t="inlineStr">
+        <is>
+          <t>Case Study/Examples archetype; De Beers angle distinct from No.28's legal/economic comparison framing. FAQ included.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Production Trackers/MPLY_Article_Production.xlsx
+++ b/Production Trackers/MPLY_Article_Production.xlsx
@@ -5688,22 +5688,22 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Omit</t>
+          <t>Contextual Section (revised 2026-09-24: Omit retired, comprehensive MPLY now mandatory)</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>None (per brief; respected)</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; no verified numeric dataset warranted without fabricating accrual figures.</t>
+          <t>Illustrative net-income-vs-operating-cash-flow line chart (accrual gap concept), labeled illustrative.</t>
         </is>
       </c>
       <c r="R46" s="4" t="inlineStr"/>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>#EarningsQuality #QualityInvesting #Accounting #FundamentalAnalysis #Investing</t>
+          <t>#EarningsQuality #QualityInvesting #Accounting #FundamentalAnalysis #MPLY #Investing</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>Explainer archetype.</t>
+          <t>Explainer archetype. MPLY angle: earnings quality as a complementary diligence check on MPLY holdings' reported margins.</t>
         </is>
       </c>
     </row>
@@ -5799,22 +5799,22 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Omit</t>
+          <t>Contextual Section (revised 2026-09-24)</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>None (per brief; respected)</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; formula explained clearly in prose, no chart warranted.</t>
+          <t>Illustrative DIO+DSO-DPO cash conversion cycle breakdown chart, labeled illustrative.</t>
         </is>
       </c>
       <c r="R47" s="4" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
-          <t>#CashConversionCycle #WorkingCapital #BusinessEconomics #Investing #Fundamentals</t>
+          <t>#CashConversionCycle #WorkingCapital #BusinessEconomics #MPLY #Investing #Fundamentals</t>
         </is>
       </c>
       <c r="U47" s="4" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>Explainer archetype.</t>
+          <t>Explainer archetype. MPLY angle: favorable cash conversion cycles as corroborating evidence of pricing power/industry concentration.</t>
         </is>
       </c>
     </row>
@@ -5910,22 +5910,22 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Omit</t>
+          <t>Contextual Section (revised 2026-09-24)</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>None (per brief; respected)</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; mechanism explained clearly in prose, no chart warranted.</t>
+          <t>Illustrative profit-swing-by-cost-structure bar chart, labeled illustrative.</t>
         </is>
       </c>
       <c r="R48" s="4" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>#OperatingLeverage #BusinessEconomics #Profitability #Investing #Fundamentals</t>
+          <t>#OperatingLeverage #BusinessEconomics #Profitability #MPLY #Investing #Fundamentals</t>
         </is>
       </c>
       <c r="U48" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>Mechanism-Based archetype.</t>
+          <t>Mechanism-Based archetype. MPLY angle: dominant/scaled businesses often carry high operating leverage, cuts both ways as a risk factor.</t>
         </is>
       </c>
     </row>
@@ -6026,17 +6026,17 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>Brief Mention</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; formula and concept clear in prose without a chart.</t>
+          <t>Illustrative revenue-to-operating-profit margin waterfall chart (shared with No.48), labeled illustrative.</t>
         </is>
       </c>
       <c r="R49" s="4" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="T49" s="4" t="inlineStr">
         <is>
-          <t>#GrossMargin #QualityInvesting #PricingPower #Investing #Fundamentals</t>
+          <t>#GrossMargin #QualityInvesting #PricingPower #MPLY #Investing #Fundamentals</t>
         </is>
       </c>
       <c r="U49" s="4" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>Brief Mention</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; concept clear in prose without a chart.</t>
+          <t>Illustrative revenue-to-operating-profit margin waterfall chart (shared with No.47), labeled illustrative.</t>
         </is>
       </c>
       <c r="R50" s="4" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>#OperatingMargin #QualityInvesting #Profitability #Investing #Fundamentals</t>
+          <t>#OperatingMargin #QualityInvesting #Profitability #MPLY #Investing #Fundamentals</t>
         </is>
       </c>
       <c r="U50" s="4" t="inlineStr">
@@ -6256,17 +6256,17 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>Brief Mention (per brief; expanded)</t>
+          <t>Contextual Section (expanded)</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; conceptual, no chart warranted.</t>
+          <t>Illustrative churn-vs-lifetime-value sensitivity chart (shared with No.50, No.51), labeled illustrative.</t>
         </is>
       </c>
       <c r="R51" s="4" t="inlineStr">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>Brief Mention</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; conceptual, no chart warranted.</t>
+          <t>Illustrative churn-vs-lifetime-value sensitivity chart (shared with No.49, No.51), labeled illustrative.</t>
         </is>
       </c>
       <c r="R52" s="4" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>#SubscriptionBusiness #BusinessModels #RecurringRevenue #Churn #Investing</t>
+          <t>#SubscriptionBusiness #BusinessModels #RecurringRevenue #Churn #MPLY #Investing</t>
         </is>
       </c>
       <c r="U52" s="4" t="inlineStr">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>Brief Mention</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; formula clear in prose without a chart.</t>
+          <t>Illustrative churn-vs-lifetime-value sensitivity chart (shared with No.49, No.50), labeled illustrative.</t>
         </is>
       </c>
       <c r="R53" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="T53" s="4" t="inlineStr">
         <is>
-          <t>#CustomerLifetimeValue #BusinessEconomics #Retention #Investing #Fundamentals</t>
+          <t>#CustomerLifetimeValue #BusinessEconomics #Retention #MPLY #Investing #Fundamentals</t>
         </is>
       </c>
       <c r="U53" s="4" t="inlineStr">
@@ -6596,22 +6596,22 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Omit</t>
+          <t>Contextual Section (revised 2026-09-24)</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>None (per brief; respected)</t>
+          <t>Contextual Section</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>Evaluated; ratio/payback concepts clear in prose without a chart.</t>
+          <t>Illustrative LTV:CAC ratio benchmark chart, labeled illustrative.</t>
         </is>
       </c>
       <c r="R54" s="4" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>#CAC #CustomerLifetimeValue #UnitEconomics #BusinessEconomics #Investing</t>
+          <t>#CAC #CustomerLifetimeValue #UnitEconomics #BusinessEconomics #MPLY #Investing</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>Comparison archetype.</t>
+          <t>Comparison archetype. MPLY angle: dominant companies typically show stronger LTV:CAC ratios via lower paid-acquisition dependence.</t>
         </is>
       </c>
     </row>
